--- a/artfynd/A 63628-2020 artfynd.xlsx
+++ b/artfynd/A 63628-2020 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 63628-2020 artfynd.xlsx
+++ b/artfynd/A 63628-2020 artfynd.xlsx
@@ -8009,10 +8009,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>119584315</v>
+        <v>119585393</v>
       </c>
       <c r="B67" t="n">
-        <v>89222</v>
+        <v>91832</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -8021,41 +8021,41 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>245031</v>
+        <v>4361</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Borgsjömusseron</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Tricholoma borgsjoeënse</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>Jacobsson &amp; Muskos</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
-          <t>Svensbergsbäcken, Jmt</t>
+          <t>Renkullmyren, Renkullmyren, Jmt</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>446765</v>
+        <v>446693</v>
       </c>
       <c r="R67" t="n">
-        <v>7032865</v>
+        <v>7032620</v>
       </c>
       <c r="S67" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -8082,19 +8082,9 @@
           <t>2024-09-06</t>
         </is>
       </c>
-      <c r="Z67" t="inlineStr">
-        <is>
-          <t>15:15</t>
-        </is>
-      </c>
       <c r="AA67" t="inlineStr">
         <is>
           <t>2024-09-06</t>
-        </is>
-      </c>
-      <c r="AB67" t="inlineStr">
-        <is>
-          <t>15:15</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -8109,22 +8099,22 @@
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Anders Hildingsson</t>
+          <t>Rashid Kadhim</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Anders Hildingsson, Johan Staaf, Rashid Kadhim</t>
+          <t>Rashid Kadhim, Johan Staaf, Anders Hildingsson</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>119585393</v>
+        <v>119584315</v>
       </c>
       <c r="B68" t="n">
-        <v>91832</v>
+        <v>89222</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -8133,41 +8123,41 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>4361</v>
+        <v>245031</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Borgsjömusseron</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Tricholoma borgsjoeënse</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>Jacobsson &amp; Muskos</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
-          <t>Renkullmyren, Renkullmyren, Jmt</t>
+          <t>Svensbergsbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>446693</v>
+        <v>446765</v>
       </c>
       <c r="R68" t="n">
-        <v>7032620</v>
+        <v>7032865</v>
       </c>
       <c r="S68" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>
@@ -8194,9 +8184,19 @@
           <t>2024-09-06</t>
         </is>
       </c>
+      <c r="Z68" t="inlineStr">
+        <is>
+          <t>15:15</t>
+        </is>
+      </c>
       <c r="AA68" t="inlineStr">
         <is>
           <t>2024-09-06</t>
+        </is>
+      </c>
+      <c r="AB68" t="inlineStr">
+        <is>
+          <t>15:15</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -8211,12 +8211,12 @@
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Rashid Kadhim</t>
+          <t>Anders Hildingsson</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Rashid Kadhim, Johan Staaf, Anders Hildingsson</t>
+          <t>Anders Hildingsson, Johan Staaf, Rashid Kadhim</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>

--- a/artfynd/A 63628-2020 artfynd.xlsx
+++ b/artfynd/A 63628-2020 artfynd.xlsx
@@ -8009,10 +8009,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>119585393</v>
+        <v>119584315</v>
       </c>
       <c r="B67" t="n">
-        <v>91832</v>
+        <v>89222</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -8021,41 +8021,41 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>4361</v>
+        <v>245031</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Borgsjömusseron</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Tricholoma borgsjoeënse</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>Jacobsson &amp; Muskos</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
-          <t>Renkullmyren, Renkullmyren, Jmt</t>
+          <t>Svensbergsbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>446693</v>
+        <v>446765</v>
       </c>
       <c r="R67" t="n">
-        <v>7032620</v>
+        <v>7032865</v>
       </c>
       <c r="S67" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -8082,9 +8082,19 @@
           <t>2024-09-06</t>
         </is>
       </c>
+      <c r="Z67" t="inlineStr">
+        <is>
+          <t>15:15</t>
+        </is>
+      </c>
       <c r="AA67" t="inlineStr">
         <is>
           <t>2024-09-06</t>
+        </is>
+      </c>
+      <c r="AB67" t="inlineStr">
+        <is>
+          <t>15:15</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -8099,22 +8109,22 @@
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Rashid Kadhim</t>
+          <t>Anders Hildingsson</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Rashid Kadhim, Johan Staaf, Anders Hildingsson</t>
+          <t>Anders Hildingsson, Johan Staaf, Rashid Kadhim</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>119584315</v>
+        <v>119585393</v>
       </c>
       <c r="B68" t="n">
-        <v>89222</v>
+        <v>91832</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -8123,41 +8133,41 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>245031</v>
+        <v>4361</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Borgsjömusseron</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Tricholoma borgsjoeënse</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>Jacobsson &amp; Muskos</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
-          <t>Svensbergsbäcken, Jmt</t>
+          <t>Renkullmyren, Renkullmyren, Jmt</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>446765</v>
+        <v>446693</v>
       </c>
       <c r="R68" t="n">
-        <v>7032865</v>
+        <v>7032620</v>
       </c>
       <c r="S68" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>
@@ -8184,19 +8194,9 @@
           <t>2024-09-06</t>
         </is>
       </c>
-      <c r="Z68" t="inlineStr">
-        <is>
-          <t>15:15</t>
-        </is>
-      </c>
       <c r="AA68" t="inlineStr">
         <is>
           <t>2024-09-06</t>
-        </is>
-      </c>
-      <c r="AB68" t="inlineStr">
-        <is>
-          <t>15:15</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -8211,12 +8211,12 @@
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Anders Hildingsson</t>
+          <t>Rashid Kadhim</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Anders Hildingsson, Johan Staaf, Rashid Kadhim</t>
+          <t>Rashid Kadhim, Johan Staaf, Anders Hildingsson</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>

--- a/artfynd/A 63628-2020 artfynd.xlsx
+++ b/artfynd/A 63628-2020 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY68"/>
+  <dimension ref="A1:AY69"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8221,6 +8221,112 @@
       </c>
       <c r="AY68" t="inlineStr"/>
     </row>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>120431881</v>
+      </c>
+      <c r="B69" t="n">
+        <v>89270</v>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E69" t="n">
+        <v>1599</v>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>Fjällfotad musseron</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>Tricholoma olivaceotinctum</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>Mort.Chr. &amp; Heilm.-Claus.</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr"/>
+      <c r="J69" t="inlineStr"/>
+      <c r="K69" t="inlineStr"/>
+      <c r="N69" t="inlineStr"/>
+      <c r="P69" t="inlineStr">
+        <is>
+          <t>Prostbölestigen väster om Renkullmyren, Jmt</t>
+        </is>
+      </c>
+      <c r="Q69" t="n">
+        <v>446655</v>
+      </c>
+      <c r="R69" t="n">
+        <v>7032527</v>
+      </c>
+      <c r="S69" t="n">
+        <v>10</v>
+      </c>
+      <c r="T69" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U69" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V69" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W69" t="inlineStr">
+        <is>
+          <t>Alsen</t>
+        </is>
+      </c>
+      <c r="Y69" t="inlineStr">
+        <is>
+          <t>2024-09-06</t>
+        </is>
+      </c>
+      <c r="AA69" t="inlineStr">
+        <is>
+          <t>2024-09-06</t>
+        </is>
+      </c>
+      <c r="AD69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF69" t="inlineStr"/>
+      <c r="AG69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT69" t="inlineStr"/>
+      <c r="AW69" t="inlineStr">
+        <is>
+          <t>Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AX69" t="inlineStr">
+        <is>
+          <t>Johan Staaf, Anders Hildingsson, Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AY69" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
